--- a/course-design-2/outputs/tables/ch3/56_stage26_6_figure_retention_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/56_stage26_6_figure_retention_audit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_逐图审计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_结论统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="01_逐图审计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_结论统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据口径是否为最终版本</t>
+          <t>数据统计范围是否为最终版本</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -549,23 +549,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>supplementary/fig_s16_acquisition_flow.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4382 × 2405</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1060.2</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -575,7 +571,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>最终口径（采集阶段无统计量）</t>
+          <t>最终统计范围（采集阶段无统计量）</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -585,7 +581,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>采集阶段唯一的流程证据，与表 3-1 的字段口径互补；图内无统计数字，不受口径变化影响</t>
+          <t>采集阶段唯一的流程证据，与表 3-1 的字段统计范围互补；图内无统计数字，不受统计范围变化影响</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -632,23 +628,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>sci/fig_01_data_governance_job_version_flow.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4310 × 2906</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1042.7</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -658,7 +650,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -710,28 +702,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>是：表 3-2 与表 4-2 已给出全部口径与样本量</t>
+          <t>是：表 3-2 与表 4-2 已给出全部统计范围与样本量</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>sci/fig_02_raw_observation_entity_compression.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4253 × 1899</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1029</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -741,7 +729,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -773,7 +761,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>正式分析样本与技能提取口径结构</t>
+          <t>正式薪资分析样本与岗位描述处理结果</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -783,7 +771,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>给出样本口径层级与技能提取三口径的规模对照</t>
+          <t>给出进入薪资分析的岗位样本构成与岗位描述形成技能信息的规模对照</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -798,23 +786,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>supplementary/fig_s34_formal_sample_skill_extraction_structure.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3328 × 2910</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>545.4</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -824,7 +808,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -834,7 +818,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>口径对照本身是第 4 章的分析起点，但图内注释框与表 3-2 逐项重复；按提示词只保留「唯一岗位实体 / 薪资可解析 / 正式薪资样本 / 技能主口径 / 技能扩展口径 / 无可用技能文本」六项标签</t>
+          <t>两部分关系是第 4 章的分析起点：左图回答「哪些岗位进入薪资分析」，右图回答「岗位描述如何形成技能信息」；但图内注释框与表 3-2 逐项重复，故按提示词只保留「唯一岗位 / 明确薪资可解析 / 纳入薪资分析 / 明确要求段落匹配 / 全文补充匹配 / 缺少可解析岗位描述」六项标签，并统一为「样本构成 + 技能文本可用性」表述，避免「层级 / 统计范围」这类偏方法说明的词</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -844,7 +828,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>fig_s69_formal_sample_skill_extraction_structure</t>
+          <t>fig_4_1_formal_sample_jd_processing_result</t>
         </is>
       </c>
     </row>
@@ -881,23 +865,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>eda/03_category_salary.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3827 × 2450</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>925.9</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -907,7 +887,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>最终口径（29 号表 03_岗位因素薪资）</t>
+          <t>最终统计范围（29 号表 03_岗位因素薪资）</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -927,7 +907,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>fig_s70_main_subcategory_salary_quartile</t>
+          <t>fig_4_3_main_subcategory_salary_quartile</t>
         </is>
       </c>
     </row>
@@ -964,23 +944,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>supplementary/图S66_互联网IT实习岗位样本的省域分布.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4048 × 3334</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>663.4</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1000,7 +976,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>样本空间结构的唯一证据；口径已在正文明确为 17,144 个唯一岗位实体，与 14,883 个正式薪资样本区分，分级依据为分位点</t>
+          <t>样本空间结构的唯一证据；统计范围已在正文明确为 17,144 个唯一岗位实体，与 14,883 个正式薪资样本区分，分级依据为分位点</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1047,23 +1023,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>supplementary/fig_s55_salary_midpoint_distribution.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2391 × 3217</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>578.5</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1073,7 +1045,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>最终口径（14,883）</t>
+          <t>最终统计范围（14,883）</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1105,7 +1077,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>招聘周期持续时长分布与累积分布（严格口径）</t>
+          <t>招聘周期持续时长分布与累积分布（严格统计范围）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1115,7 +1087,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>给出严格口径计划持续时长的分布与累积</t>
+          <t>给出严格统计范围计划持续时长的分布与累积</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1130,23 +1102,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>supplementary/fig_s50_recruitment_duration_distribution.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3351 × 3725</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>549.2</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1156,7 +1124,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>最终口径（严格口径 17,131）</t>
+          <t>最终统计范围（严格统计范围 17,131）</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1208,28 +1176,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>是：表 4-2 与表 4-2 的口径行已给出序列口径与规模</t>
+          <t>是：表 4-2 与表 4-2 的统计范围行已给出序列统计范围与规模</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>supplementary/图S67_样本计划招聘覆盖每日活跃计划周期数量.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3330 × 1988</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>545.7</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1239,7 +1203,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1249,7 +1213,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>该序列的全部关键数值已在正文与表 4-2 给出，图仅为同一序列的平滑曲线；其口径已在 4.5.2 两次声明「非市场存量」，属样本派生描述，删除后 4.5.2 的结论链完整</t>
+          <t>该序列的全部关键数值已在正文与表 4-2 给出，图仅为同一序列的平滑曲线；其统计范围已在 4.5.2 两次声明「非市场存量」，属样本派生描述，删除后 4.5.2 的结论链完整</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1291,28 +1255,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>部分：表 4-2、表 4-3 承担阈值与总体口径</t>
+          <t>部分：表 4-2、表 4-3 承担阈值与总体范围</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>supplementary/fig_s57_main_category_planned_coverage.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3426 × 2320</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>561.4</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1322,7 +1282,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>最终口径（按多值大类命中即计入）</t>
+          <t>最终统计范围（按多值大类命中即计入）</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1379,23 +1339,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>supplementary/fig_s58_active_cycle_salary_median_iqr.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3173 × 2189</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>520</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1405,7 +1361,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>最终口径（Strict 日级面板）</t>
+          <t>最终统计范围（Strict 日级面板）</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1425,7 +1381,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>fig_s71_active_cycle_salary_quartile</t>
+          <t>fig_4_7_active_cycle_salary_quartile</t>
         </is>
       </c>
     </row>
@@ -1462,23 +1418,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>supplementary/fig_s59_city_education_company_size_salary.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2502 × 3762</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>605.3</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1488,7 +1440,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>最终口径（14,883）</t>
+          <t>最终统计范围（14,883）</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1545,23 +1497,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>supplementary/fig_s60_certification_salary_distribution.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3409 × 3095</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>558.7</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1571,7 +1519,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1628,23 +1576,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>supplementary/fig_s61_benefit_label_salary_effect.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3759 × 2521</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>616</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1654,7 +1598,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1711,23 +1655,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>supplementary/fig_s62_high_effect_benefit_label_cluster.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3935 × 3531</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>644.9</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1737,7 +1677,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1769,7 +1709,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>核心技术技能需求 Top20（技能主口径，分母 8,822）</t>
+          <t>核心技术技能需求 Top20（技能主统计范围，分母 8,822）</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1794,23 +1734,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>eda/fig_05_tech_skill_top20.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3505 × 2613</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>848</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1820,7 +1756,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>最终口径（主口径 8,822）</t>
+          <t>最终统计范围（主统计范围 8,822）</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1877,23 +1813,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>supplementary/fig_s63_category_skill_hit_heatmap.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3963 × 3398</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>649.5</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1903,7 +1835,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>最终口径（细分类内部命中率）</t>
+          <t>最终统计范围（细分类内部命中率）</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1960,23 +1892,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>eda/08_skill_cooccurrence.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3284 × 2823</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>794.5</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1986,7 +1914,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2038,28 +1966,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>部分：表 6-1 给出未控制口径的 δ</t>
+          <t>部分：表 6-1 给出未控制统计范围的 δ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>supplementary/fig_s09_skill_salary_control_dumbbell.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4654 × 2629</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1126</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2069,7 +1993,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>最终口径（控制前后两口径并列）</t>
+          <t>最终统计范围（控制前后两种统计范围并列）</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2079,7 +2003,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>「部分差异来自岗位类别」是本轮技能结论的关键限定，该图是唯一并列证据；表 6-1 只承载未控制口径</t>
+          <t>「部分差异来自岗位类别」是本轮技能结论的关键限定，该图是唯一并列证据；表 6-1 只承载未控制统计范围</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2126,23 +2050,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>supplementary/fig_s48_salary_model_build_eval_flow.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2414 × 3863</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>584</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2152,7 +2072,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2172,7 +2092,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>fig_s72_salary_model_build_eval_flow（节点简化）</t>
+          <t>fig_s72_salary_model_build_eval_flow</t>
         </is>
       </c>
     </row>
@@ -2209,23 +2129,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>supplementary/fig_s51_feature_group_ablation_comparison.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3297 × 2061</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>540.3</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2235,7 +2151,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2255,7 +2171,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>图S73_特征组消融实验的验证集与测试集MAE（横轴标签简化）</t>
+          <t>fig_s73_feature_group_ablation_test_mae</t>
         </is>
       </c>
     </row>
@@ -2292,23 +2208,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>supplementary/fig_s64_shap_beeswarm.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3656 × 3667</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>743</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2318,7 +2230,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>最终口径（最终主模型 + 同一测试集）</t>
+          <t>最终统计范围（最终主模型 + 同一测试集）</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2375,23 +2287,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>supplementary/fig_s68_skill_shap_contribution.png</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3395 × 2609</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>749.9</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
+          <t>需检查</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2401,7 +2309,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>最终口径</t>
+          <t>最终统计范围</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">

--- a/course-design-2/outputs/tables/ch3/56_stage26_6_figure_retention_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/56_stage26_6_figure_retention_audit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_逐图审计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_结论统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_逐图审计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_结论统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,19 +549,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s16_acquisition_flow.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>4382 × 2405</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1060.2</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -571,7 +575,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>最终统计范围（采集阶段无统计量）</t>
+          <t>最终口径（采集阶段无统计量）</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -581,7 +585,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>采集阶段唯一的流程证据，与表 3-1 的字段统计范围互补；图内无统计数字，不受统计范围变化影响</t>
+          <t>采集阶段唯一的流程证据，与表 3-1 的字段口径互补；图内无统计数字，不受口径变化影响</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -628,19 +632,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>sci/fig_01_data_governance_job_version_flow.png</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>4310 × 2906</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1042.7</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -650,7 +658,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -702,24 +710,28 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>是：表 3-2 与表 4-2 已给出全部统计范围与样本量</t>
+          <t>是：表 3-2 与表 4-2 已给出全部口径与样本量</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>sci/fig_02_raw_observation_entity_compression.png</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>4253 × 1899</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1029</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -729,7 +741,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -761,7 +773,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>正式薪资分析样本与岗位描述处理结果</t>
+          <t>正式分析样本与技能提取口径结构</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -771,7 +783,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>给出进入薪资分析的岗位样本构成与岗位描述形成技能信息的规模对照</t>
+          <t>给出样本口径层级与技能提取三口径的规模对照</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -786,19 +798,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s34_formal_sample_skill_extraction_structure.png</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>3328 × 2910</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>545.4</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -808,7 +824,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -818,7 +834,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>两部分关系是第 4 章的分析起点：左图回答「哪些岗位进入薪资分析」，右图回答「岗位描述如何形成技能信息」；但图内注释框与表 3-2 逐项重复，故按提示词只保留「唯一岗位 / 明确薪资可解析 / 纳入薪资分析 / 明确要求段落匹配 / 全文补充匹配 / 缺少可解析岗位描述」六项标签，并统一为「样本构成 + 技能文本可用性」表述，避免「层级 / 统计范围」这类偏方法说明的词</t>
+          <t>口径对照本身是第 4 章的分析起点，但图内注释框与表 3-2 逐项重复；按提示词只保留「唯一岗位实体 / 薪资可解析 / 正式薪资样本 / 技能主口径 / 技能扩展口径 / 无可用技能文本」六项标签</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -828,7 +844,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>fig_4_1_formal_sample_jd_processing_result</t>
+          <t>fig_s69_formal_sample_skill_extraction_structure</t>
         </is>
       </c>
     </row>
@@ -865,19 +881,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>eda/03_category_salary.png</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>3827 × 2450</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>925.9</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -887,7 +907,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>最终统计范围（29 号表 03_岗位因素薪资）</t>
+          <t>最终口径（29 号表 03_岗位因素薪资）</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -907,7 +927,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>fig_4_3_main_subcategory_salary_quartile</t>
+          <t>fig_s70_main_subcategory_salary_quartile</t>
         </is>
       </c>
     </row>
@@ -944,19 +964,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/图S66_互联网IT实习岗位样本的省域分布.png</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>4048 × 3334</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>663.4</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -976,7 +1000,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>样本空间结构的唯一证据；统计范围已在正文明确为 17,144 个唯一岗位实体，与 14,883 个正式薪资样本区分，分级依据为分位点</t>
+          <t>样本空间结构的唯一证据；口径已在正文明确为 17,144 个唯一岗位实体，与 14,883 个正式薪资样本区分，分级依据为分位点</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1023,19 +1047,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s55_salary_midpoint_distribution.png</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>2391 × 3217</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>578.5</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1045,7 +1073,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>最终统计范围（14,883）</t>
+          <t>最终口径（14,883）</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1077,7 +1105,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>招聘周期持续时长分布与累积分布（严格统计范围）</t>
+          <t>招聘周期持续时长分布与累积分布（严格口径）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1087,7 +1115,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>给出严格统计范围计划持续时长的分布与累积</t>
+          <t>给出严格口径计划持续时长的分布与累积</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1102,19 +1130,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s50_recruitment_duration_distribution.png</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>3351 × 3725</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>549.2</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1124,7 +1156,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>最终统计范围（严格统计范围 17,131）</t>
+          <t>最终口径（严格口径 17,131）</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1176,24 +1208,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>是：表 4-2 与表 4-2 的统计范围行已给出序列统计范围与规模</t>
+          <t>是：表 4-2 与表 4-2 的口径行已给出序列口径与规模</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/图S67_样本计划招聘覆盖每日活跃计划周期数量.png</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>3330 × 1988</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>545.7</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1203,7 +1239,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1213,7 +1249,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>该序列的全部关键数值已在正文与表 4-2 给出，图仅为同一序列的平滑曲线；其统计范围已在 4.5.2 两次声明「非市场存量」，属样本派生描述，删除后 4.5.2 的结论链完整</t>
+          <t>该序列的全部关键数值已在正文与表 4-2 给出，图仅为同一序列的平滑曲线；其口径已在 4.5.2 两次声明「非市场存量」，属样本派生描述，删除后 4.5.2 的结论链完整</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1255,24 +1291,28 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>部分：表 4-2、表 4-3 承担阈值与总体范围</t>
+          <t>部分：表 4-2、表 4-3 承担阈值与总体口径</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s57_main_category_planned_coverage.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>3426 × 2320</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>561.4</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1282,7 +1322,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>最终统计范围（按多值大类命中即计入）</t>
+          <t>最终口径（按多值大类命中即计入）</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1339,19 +1379,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s58_active_cycle_salary_median_iqr.png</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>3173 × 2189</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>520</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1361,7 +1405,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>最终统计范围（Strict 日级面板）</t>
+          <t>最终口径（Strict 日级面板）</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1381,7 +1425,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>fig_4_7_active_cycle_salary_quartile</t>
+          <t>fig_s71_active_cycle_salary_quartile</t>
         </is>
       </c>
     </row>
@@ -1418,19 +1462,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s59_city_education_company_size_salary.png</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>2502 × 3762</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>605.3</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1440,7 +1488,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>最终统计范围（14,883）</t>
+          <t>最终口径（14,883）</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1497,19 +1545,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s60_certification_salary_distribution.png</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>3409 × 3095</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>558.7</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1519,7 +1571,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1576,19 +1628,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s61_benefit_label_salary_effect.png</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>3759 × 2521</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>616</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1598,7 +1654,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1655,19 +1711,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s62_high_effect_benefit_label_cluster.png</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>3935 × 3531</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>644.9</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1677,7 +1737,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1709,7 +1769,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>核心技术技能需求 Top20（技能主统计范围，分母 8,822）</t>
+          <t>核心技术技能需求 Top20（技能主口径，分母 8,822）</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1734,19 +1794,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>eda/fig_05_tech_skill_top20.png</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>3505 × 2613</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>848</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1756,7 +1820,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>最终统计范围（主统计范围 8,822）</t>
+          <t>最终口径（主口径 8,822）</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1813,19 +1877,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s63_category_skill_hit_heatmap.png</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>3963 × 3398</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>649.5</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1835,7 +1903,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>最终统计范围（细分类内部命中率）</t>
+          <t>最终口径（细分类内部命中率）</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1892,19 +1960,23 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>eda/08_skill_cooccurrence.png</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>3284 × 2823</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>794.5</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1914,7 +1986,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1966,24 +2038,28 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>部分：表 6-1 给出未控制统计范围的 δ</t>
+          <t>部分：表 6-1 给出未控制口径的 δ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s09_skill_salary_control_dumbbell.png</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>4654 × 2629</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1126</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1993,7 +2069,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>最终统计范围（控制前后两种统计范围并列）</t>
+          <t>最终口径（控制前后两口径并列）</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2003,7 +2079,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>「部分差异来自岗位类别」是本轮技能结论的关键限定，该图是唯一并列证据；表 6-1 只承载未控制统计范围</t>
+          <t>「部分差异来自岗位类别」是本轮技能结论的关键限定，该图是唯一并列证据；表 6-1 只承载未控制口径</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2050,19 +2126,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s48_salary_model_build_eval_flow.png</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>2414 × 3863</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>584</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2072,7 +2152,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2092,7 +2172,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>fig_s72_salary_model_build_eval_flow</t>
+          <t>fig_s72_salary_model_build_eval_flow（节点简化）</t>
         </is>
       </c>
     </row>
@@ -2129,19 +2209,23 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s51_feature_group_ablation_comparison.png</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>3297 × 2061</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>540.3</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2151,7 +2235,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2171,7 +2255,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>fig_s73_feature_group_ablation_test_mae</t>
+          <t>图S73_特征组消融实验的验证集与测试集MAE（横轴标签简化）</t>
         </is>
       </c>
     </row>
@@ -2208,19 +2292,23 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s64_shap_beeswarm.png</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>3656 × 3667</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>743</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2230,7 +2318,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>最终统计范围（最终主模型 + 同一测试集）</t>
+          <t>最终口径（最终主模型 + 同一测试集）</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2287,19 +2375,23 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>supplementary/fig_s68_skill_shap_contribution.png</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>3395 × 2609</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>749.9</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>需检查</t>
+          <t>达标：有效分辨率 ≥ 520 dpi，图内无长句</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2309,7 +2401,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>最终统计范围</t>
+          <t>最终口径</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
